--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488179_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488179_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9588</v>
+        <v>6.8866</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1293</v>
+        <v>5.8355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8295</v>
+        <v>1.0511</v>
       </c>
       <c r="G2" t="n">
         <v>8.0152</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1681</v>
+        <v>-0.2403</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1231</v>
+        <v>-0.1706</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2913</v>
+        <v>-0.0697</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2589</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1401</v>
+        <v>1.7769</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7783</v>
+        <v>-0.1907</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9183</v>
+        <v>1.9676</v>
       </c>
       <c r="G3" t="n">
         <v>2.9688</v>
@@ -688,13 +688,13 @@
         <v>1.4823</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5317</v>
+        <v>0.1051</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9637</v>
+        <v>-0.3761</v>
       </c>
       <c r="U3" t="n">
-        <v>0.432</v>
+        <v>0.4812</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. NDIAYE</t>
+          <t>M. MALICK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0465</v>
+        <v>-0.3459</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4296</v>
+        <v>-1.0584</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4761</v>
+        <v>0.7125</v>
       </c>
       <c r="G6" t="n">
-        <v>2.161</v>
+        <v>-1.8137</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5203</v>
+        <v>0.5809</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3593</v>
+        <v>-2.3947</v>
       </c>
       <c r="J6" t="n">
-        <v>1.928</v>
+        <v>0.0332</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8036</v>
+        <v>0.5925</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1244</v>
+        <v>-0.5592</v>
       </c>
       <c r="M6" t="n">
-        <v>0.233</v>
+        <v>-1.847</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7167</v>
+        <v>-0.0115</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4837</v>
+        <v>-1.8354</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.297</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.2234</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9772</v>
+        <v>-0.2537</v>
       </c>
       <c r="T6" t="n">
-        <v>0.725</v>
+        <v>-0.4414</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2522</v>
+        <v>0.1878</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.8877</v>
+        <v>2.8332</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8877</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. MALICK</t>
+          <t>S. VICENTE GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3705</v>
+        <v>-0.3947</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0584</v>
+        <v>-0.5487</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6878</v>
+        <v>0.154</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8137</v>
+        <v>1.2931</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5809</v>
+        <v>0.1196</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.3947</v>
+        <v>1.1735</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0332</v>
+        <v>0.7386</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5925</v>
+        <v>0.0644</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5592</v>
+        <v>0.6742</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.847</v>
+        <v>0.5544</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0115</v>
+        <v>0.0552</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8354</v>
+        <v>0.4993</v>
       </c>
       <c r="P7" t="n">
+        <v>-0.9264</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-1.1117</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-2.2234</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.1117</v>
+        <v>0.1853</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2783</v>
+        <v>-0.7614</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4414</v>
+        <v>-0.1756</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1631</v>
+        <v>-0.5857</v>
       </c>
       <c r="V7" t="n">
-        <v>2.8332</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. VICENTE GARCIA</t>
+          <t>T. GARRETT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6896</v>
+        <v>-0.7685</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.5387</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.043</v>
+        <v>-0.2298</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2931</v>
+        <v>-1.1438</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1196</v>
+        <v>-0.8182</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1735</v>
+        <v>-0.3256</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7386</v>
+        <v>-0.4104</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0644</v>
+        <v>-0.5455</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6742</v>
+        <v>0.1351</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5544</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0552</v>
+        <v>-0.2727</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4993</v>
+        <v>-0.4607</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.1853</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-0.9264</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.1117</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.1853</v>
+        <v>0.7411</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0563</v>
+        <v>-0.6983</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2736</v>
+        <v>-0.4607</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7827</v>
+        <v>-0.2375</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. GARRETT</t>
+          <t>B. CATALDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8905</v>
+        <v>-1.0137</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7346</v>
+        <v>-0.8522</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1559</v>
+        <v>-0.1615</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1438</v>
+        <v>0.0324</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8182</v>
+        <v>-0.1643</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3256</v>
+        <v>0.1967</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4104</v>
+        <v>0.9805</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5455</v>
+        <v>0.1926</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1351</v>
+        <v>0.788</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2727</v>
+        <v>-0.3568</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4607</v>
+        <v>-0.5913</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8202</v>
+        <v>-0.1023</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6566</v>
+        <v>-0.2764</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1637</v>
+        <v>0.1741</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2589</v>
+        <v>-0.9439</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2589</v>
+        <v>-0.63</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.3139</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. QUINTA RAMOS</t>
+          <t>F. NDIAYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0548</v>
+        <v>-1.1008</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9643</v>
+        <v>-0.3539</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0905</v>
+        <v>-0.7469</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7974</v>
+        <v>2.161</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.1953</v>
+        <v>2.5203</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3979</v>
+        <v>-0.3593</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1247</v>
+        <v>1.928</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1769</v>
+        <v>1.8036</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0522</v>
+        <v>0.1244</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6727</v>
+        <v>0.233</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0184</v>
+        <v>0.7167</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3457</v>
+        <v>-0.4837</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3706</v>
+        <v>-1.297</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1853</v>
+        <v>-2.2234</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.9264</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3721</v>
+        <v>-0.0771</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3457</v>
+        <v>-0.0584</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0263</v>
+        <v>-0.0187</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.8877</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. CATALDO</t>
+          <t>J. QUINTA RAMOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3556</v>
+        <v>-1.545</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3419</v>
+        <v>-1.356</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0138</v>
+        <v>-0.189</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0324</v>
+        <v>-1.7974</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1643</v>
+        <v>-2.1953</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1967</v>
+        <v>0.3979</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9805</v>
+        <v>-1.1247</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1926</v>
+        <v>-1.1769</v>
       </c>
       <c r="L11" t="n">
-        <v>0.788</v>
+        <v>0.0522</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-0.6727</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3568</v>
+        <v>-1.0184</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5913</v>
+        <v>0.3457</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9264</v>
+        <v>-0.1853</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9264</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4442</v>
+        <v>-0.1181</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.766</v>
+        <v>-0.046</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3218</v>
+        <v>-0.0721</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.9676</v>
+        <v>-6.7711</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.0171</v>
+        <v>-6.9192</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0496</v>
+        <v>0.1481</v>
       </c>
       <c r="G12" t="n">
         <v>-1.121</v>
@@ -1390,13 +1390,13 @@
         <v>1.6676</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3261</v>
+        <v>-0.1296</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.4318</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2037</v>
+        <v>0.3021</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2589</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.309999999999999</v>
+        <v>-2.31</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.0162</v>
+        <v>-5.0161</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7059</v>
+        <v>2.7061</v>
       </c>
       <c r="G13" t="n">
         <v>9.5608</v>
@@ -1456,7 +1456,7 @@
         <v>1.7996</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.375</v>
+        <v>-5.374999999999999</v>
       </c>
       <c r="P13" t="n">
         <v>-8.3378</v>
@@ -1468,13 +1468,13 @@
         <v>9.2643</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2756</v>
+        <v>-2.2757</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.4372</v>
+        <v>-2.437</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1614</v>
+        <v>0.1615</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2573</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. ORTEGA CARO</t>
+          <t>A. RODRIGUEZ LOPEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6014</v>
+        <v>4.1179</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0451</v>
+        <v>2.4665</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4438</v>
+        <v>1.6514</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6396</v>
+        <v>1.7217</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.9447</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7203</v>
+        <v>2.6665</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4319</v>
+        <v>2.0579</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8808</v>
+        <v>-0.524</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5511</v>
+        <v>2.5819</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7922</v>
+        <v>-0.3361</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.9614</v>
+        <v>-0.4207</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1692</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8529</v>
+        <v>1.4823</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8529</v>
+        <v>1.4823</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8911</v>
+        <v>0.2845</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3867</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5044</v>
+        <v>0.1903</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LOPEZ</t>
+          <t>M. ORTEGA CARO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3574</v>
+        <v>4.0526</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9769</v>
+        <v>3.9472</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3806</v>
+        <v>0.1054</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7217</v>
+        <v>2.6396</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9447</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6665</v>
+        <v>2.7203</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0579</v>
+        <v>4.4319</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.524</v>
+        <v>1.8808</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5819</v>
+        <v>2.5511</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3361</v>
+        <v>-1.7922</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4207</v>
+        <v>-1.9614</v>
       </c>
       <c r="O15" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.1692</v>
       </c>
       <c r="P15" t="n">
-        <v>1.4823</v>
+        <v>1.8529</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4823</v>
+        <v>1.8529</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.476</v>
+        <v>-0.4399</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3954</v>
+        <v>-0.4846</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0806</v>
+        <v>0.0448</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3165</v>
+        <v>2.9116</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6795</v>
+        <v>2.2671</v>
       </c>
       <c r="F16" t="n">
-        <v>0.637</v>
+        <v>0.6445</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4308</v>
@@ -1702,13 +1702,13 @@
         <v>2.594</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1055</v>
+        <v>-0.5105</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3467</v>
+        <v>-0.7592</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2412</v>
+        <v>0.2487</v>
       </c>
       <c r="V16" t="n">
         <v>1.2589</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1386</v>
+        <v>0.6765</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3293</v>
+        <v>-1.7003</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4679</v>
+        <v>2.3769</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6827</v>
@@ -1780,13 +1780,13 @@
         <v>2.0382</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6191</v>
+        <v>1.1571</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7783</v>
+        <v>0.4073</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8409</v>
+        <v>0.7498</v>
       </c>
       <c r="V17" t="n">
         <v>0.9433</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. RUEDA MURIEL</t>
+          <t>G. VELASCO BENITEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2686</v>
+        <v>-0.0434</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1173</v>
+        <v>0.3435</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8487</v>
+        <v>-0.3869</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4773</v>
+        <v>-0.8206</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4543</v>
+        <v>-0.773</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.023</v>
+        <v>-0.0476</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9407</v>
+        <v>0.1072</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9407</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.6742</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5366</v>
+        <v>-0.9278</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.206</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.023</v>
+        <v>-0.7219</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>0.097</v>
+        <v>0.2214</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1766</v>
+        <v>0.2363</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2736</v>
+        <v>-0.0149</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SOSA LLANO</t>
+          <t>M. RUEDA MURIEL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2981</v>
+        <v>-0.2686</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-1.1173</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2578</v>
+        <v>0.8487</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-1.4773</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4294</v>
+        <v>-1.4543</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3917</v>
+        <v>-0.023</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6529</v>
+        <v>-0.9407</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-0.9407</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6529</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1683</v>
+        <v>-0.5366</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4294</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2611</v>
+        <v>-0.023</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3377</v>
+        <v>0.097</v>
       </c>
       <c r="T19" t="n">
-        <v>0.097</v>
+        <v>-0.1766</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2407</v>
+        <v>0.2736</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. VELASCO BENITEZ</t>
+          <t>J. SOSA LLANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9745</v>
+        <v>-0.3474</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4399</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5346</v>
+        <v>0.2085</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8206</v>
+        <v>-0.8211000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.773</v>
+        <v>-0.4294</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0476</v>
+        <v>-0.3917</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1072</v>
+        <v>-0.6529</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5669999999999999</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6742</v>
+        <v>-0.6529</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9278</v>
+        <v>-0.1683</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.206</v>
+        <v>-0.4294</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7219</v>
+        <v>0.2611</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.1853</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.1853</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7098</v>
+        <v>0.2885</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5471</v>
+        <v>0.097</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1627</v>
+        <v>0.1915</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. LAGHRIDAT</t>
+          <t>J. ROBLES ROSADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0478</v>
+        <v>-1.5187</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0943</v>
+        <v>-0.0935</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0465</v>
+        <v>-1.4252</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.9557</v>
+        <v>-3.4024</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.8621</v>
+        <v>-2.5209</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0936</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1543</v>
+        <v>-0.6962</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2373</v>
+        <v>-0.1677</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0829</v>
+        <v>-0.5284</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8014</v>
+        <v>-2.7063</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6248</v>
+        <v>-2.3531</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1766</v>
+        <v>-0.3531</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1853</v>
+        <v>1.6676</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1117</v>
+        <v>1.6676</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4082</v>
+        <v>-0.0989</v>
       </c>
       <c r="T21" t="n">
-        <v>1.302</v>
+        <v>-0.0267</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1062</v>
+        <v>-0.0721</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3144</v>
+        <v>0.315</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3155</v>
+        <v>0.6294</v>
       </c>
       <c r="X21" t="n">
-        <v>0.63</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. ROBLES ROSADO</t>
+          <t>A. TEJADA CAMACHO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4512</v>
+        <v>-1.6119</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2893</v>
+        <v>-2.0925</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1619</v>
+        <v>0.4806</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.4024</v>
+        <v>-1.742</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.5209</v>
+        <v>-1.7404</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.0016</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6962</v>
+        <v>0.4792</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1677</v>
+        <v>0.3429</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5284</v>
+        <v>0.1363</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7063</v>
+        <v>-2.2212</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.3531</v>
+        <v>-2.0833</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3531</v>
+        <v>-0.138</v>
       </c>
       <c r="P22" t="n">
-        <v>1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6676</v>
+        <v>3.1499</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0313</v>
+        <v>0.7045</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2226</v>
+        <v>-0.1063</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1912</v>
+        <v>0.8108</v>
       </c>
       <c r="V22" t="n">
-        <v>0.315</v>
+        <v>-0.945</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6294</v>
+        <v>0.3139</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3144</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. TEJADA CAMACHO</t>
+          <t>S. LAGHRIDAT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0592</v>
+        <v>-2.0031</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6801</v>
+        <v>-1.9757</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6208</v>
+        <v>-0.0274</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.742</v>
+        <v>-2.9557</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.7404</v>
+        <v>-2.8621</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0016</v>
+        <v>-0.0936</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4792</v>
+        <v>-1.1543</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3429</v>
+        <v>-1.2373</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1363</v>
+        <v>0.0829</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.2212</v>
+        <v>-1.8014</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.0833</v>
+        <v>-1.6248</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.138</v>
+        <v>-0.1766</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3706</v>
+        <v>0.1853</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R23" t="n">
-        <v>3.1499</v>
+        <v>1.1117</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2572</v>
+        <v>0.453</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6939</v>
+        <v>0.4206</v>
       </c>
       <c r="U23" t="n">
-        <v>0.951</v>
+        <v>0.0323</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.945</v>
+        <v>0.3144</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3139</v>
+        <v>-0.3155</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2589</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0043</v>
+        <v>-3.0027</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9015</v>
+        <v>-4.1953</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8972</v>
+        <v>1.1926</v>
       </c>
       <c r="G24" t="n">
         <v>-1.5893</v>
@@ -2326,13 +2326,13 @@
         <v>1.8529</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7703</v>
+        <v>0.7719</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4303</v>
+        <v>0.1365</v>
       </c>
       <c r="U24" t="n">
-        <v>0.34</v>
+        <v>0.6354</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2589</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.310199999999999</v>
+        <v>2.962800000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.706099999999999</v>
+        <v>-2.706199999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>5.0162</v>
+        <v>5.6691</v>
       </c>
       <c r="G25" t="n">
         <v>-9.560600000000001</v>
@@ -2374,7 +2374,7 @@
         <v>-14.1309</v>
       </c>
       <c r="I25" t="n">
-        <v>4.570100000000001</v>
+        <v>4.5701</v>
       </c>
       <c r="J25" t="n">
         <v>3.575399999999999</v>
@@ -2383,7 +2383,7 @@
         <v>-1.7994</v>
       </c>
       <c r="L25" t="n">
-        <v>5.374699999999999</v>
+        <v>5.3747</v>
       </c>
       <c r="M25" t="n">
         <v>-13.136</v>
@@ -2392,7 +2392,7 @@
         <v>-12.3312</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8049000000000001</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P25" t="n">
         <v>8.338100000000001</v>
@@ -2404,13 +2404,13 @@
         <v>17.6024</v>
       </c>
       <c r="S25" t="n">
-        <v>2.275799999999999</v>
+        <v>2.9286</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1614</v>
+        <v>-0.1614999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>2.4371</v>
+        <v>3.0902</v>
       </c>
       <c r="V25" t="n">
         <v>1.2571</v>
